--- a/commercial/marketing/Calendrier éditorial.xlsx
+++ b/commercial/marketing/Calendrier éditorial.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CamilleTARRAY\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/theocadene/Documents/IAmi/Documents/commercial/marketing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DE78EA-FC12-47AD-AD47-F8D095FFEAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF27D75-36D0-8E45-9956-D5E6CDDF33F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F95CC3DF-3D00-496B-89A8-DBF8D39E8CDE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19860" xr2:uid="{F95CC3DF-3D00-496B-89A8-DBF8D39E8CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Calendrier éditorial" sheetId="4" r:id="rId1"/>
@@ -105,6 +105,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -145,6 +146,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -314,15 +316,15 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -343,7 +345,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -640,27 +642,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF6E60FD-18AF-4F15-B82C-7F08F742028D}">
   <dimension ref="A1:O3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.6640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" style="4" customWidth="1"/>
     <col min="3" max="3" width="18" style="7" customWidth="1"/>
-    <col min="4" max="4" width="32.5546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="32.5" style="7" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" style="5" customWidth="1"/>
     <col min="6" max="6" width="19.33203125" style="5" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" style="5" customWidth="1"/>
-    <col min="9" max="10" width="10.109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" style="5" customWidth="1"/>
+    <col min="9" max="10" width="10.1640625" style="5" customWidth="1"/>
     <col min="11" max="11" width="17" style="4" customWidth="1"/>
     <col min="12" max="12" width="40.33203125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="53.109375" style="9" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="8" customWidth="1"/>
-    <col min="15" max="15" width="44.44140625" style="8" customWidth="1"/>
-    <col min="16" max="16" width="30.44140625" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="10.88671875" style="1"/>
+    <col min="13" max="13" width="53.1640625" style="9" customWidth="1"/>
+    <col min="14" max="14" width="43.83203125" style="8" customWidth="1"/>
+    <col min="15" max="15" width="44.5" style="8" customWidth="1"/>
+    <col min="16" max="16" width="30.5" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" customFormat="1" ht="15.6">
+    <row r="1" spans="1:15" customFormat="1" ht="17">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -707,29 +709,29 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="16" customFormat="1" ht="15.6">
-      <c r="A2" s="20" t="s">
+    <row r="2" spans="1:15" s="16" customFormat="1" ht="16">
+      <c r="A2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
     </row>
-    <row r="3" spans="1:15" s="2" customFormat="1" ht="15.6">
+    <row r="3" spans="1:15" s="2" customFormat="1" ht="16">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
-      <c r="C3" s="22"/>
+      <c r="C3" s="20"/>
       <c r="D3" s="18"/>
       <c r="E3" s="14"/>
       <c r="F3" s="19"/>
@@ -738,7 +740,7 @@
       <c r="I3" s="14"/>
       <c r="J3" s="14"/>
       <c r="K3" s="13"/>
-      <c r="L3" s="23"/>
+      <c r="L3" s="21"/>
       <c r="M3" s="15"/>
       <c r="N3" s="12"/>
       <c r="O3" s="12"/>
@@ -754,26 +756,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ec301b4b-5ffe-4e81-9474-e52aed0a8ae5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ae6a1294-b038-40ea-980d-34ace42f78e7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB765B18770FCE4AABDC5BCAE7EBA4A1" ma:contentTypeVersion="14" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="104d6ede655fe99ba430314b9eaae8f9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ec301b4b-5ffe-4e81-9474-e52aed0a8ae5" xmlns:ns3="ae6a1294-b038-40ea-980d-34ace42f78e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ba1081b2bd5b4075c1566de32aa3282f" ns2:_="" ns3:_="">
     <xsd:import namespace="ec301b4b-5ffe-4e81-9474-e52aed0a8ae5"/>
@@ -986,26 +968,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE4AEEC3-3F8F-4968-9A3B-F21F8E967586}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ec301b4b-5ffe-4e81-9474-e52aed0a8ae5"/>
-    <ds:schemaRef ds:uri="ae6a1294-b038-40ea-980d-34ace42f78e7"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58DB8686-F438-4436-99C1-E227026FAA29}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ec301b4b-5ffe-4e81-9474-e52aed0a8ae5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ae6a1294-b038-40ea-980d-34ace42f78e7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60A8F221-9DE0-485A-BD7A-4930535F5DCB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1022,4 +1005,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58DB8686-F438-4436-99C1-E227026FAA29}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE4AEEC3-3F8F-4968-9A3B-F21F8E967586}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ec301b4b-5ffe-4e81-9474-e52aed0a8ae5"/>
+    <ds:schemaRef ds:uri="ae6a1294-b038-40ea-980d-34ace42f78e7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>